--- a/products/pack2-proposal-toolkit/win-theme-development.xlsx
+++ b/products/pack2-proposal-toolkit/win-theme-development.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -102,6 +102,25 @@
       <color rgb="FF01696F"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -123,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -146,6 +165,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -157,7 +190,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -258,6 +291,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -267,7 +306,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -307,6 +346,17 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -556,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="B2:J20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="17" min="1" max="1"/>
@@ -571,7 +621,6 @@
     <col width="28" customWidth="1" style="17" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="18">
       <c r="B2" s="19" t="inlineStr">
         <is>
@@ -586,7 +635,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="36" customHeight="1" s="18">
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1099,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="B2:P17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="17" min="1" max="1"/>
@@ -1109,7 +1157,6 @@
     <col width="13" customWidth="1" style="17" min="11" max="16"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="18">
       <c r="B2" s="19" t="inlineStr">
         <is>
@@ -1124,7 +1171,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="42" customHeight="1" s="18">
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1629,11 +1675,82 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>COVERAGE CHECK</t>
+        </is>
+      </c>
+      <c r="D15" s="35">
+        <f>IF(D14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>IF(E14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>IF(F14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="G15" s="35">
+        <f>IF(G14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="H15" s="35">
+        <f>IF(H14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="I15" s="35">
+        <f>IF(I14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="J15" s="35">
+        <f>IF(J14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="K15" s="35">
+        <f>IF(K14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="L15" s="35">
+        <f>IF(L14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="M15" s="35">
+        <f>IF(M14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="N15" s="35">
+        <f>IF(N14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="O15" s="35">
+        <f>IF(O14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+      <c r="P15" s="35">
+        <f>IF(P14=0,"GAP","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>GAP = no win theme maps to that evaluation factor or volume. Every weighted M factor should have at least one theme before you go to pink team.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B2:I2"/>
   </mergeCells>
+  <conditionalFormatting sqref="D15:P15">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>D15="GAP"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1647,14 +1764,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="B2:B51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="17" min="1" max="1"/>
     <col width="90" customWidth="1" style="17" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="18">
       <c r="B2" s="31" t="inlineStr">
         <is>
@@ -1669,8 +1785,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="21.75" customHeight="1" s="18">
       <c r="B6" s="32" t="inlineStr">
         <is>
@@ -1685,7 +1799,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="18" customHeight="1" s="18">
       <c r="B9" s="33" t="inlineStr">
         <is>
@@ -1714,7 +1827,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="21.75" customHeight="1" s="18">
       <c r="B14" s="32" t="inlineStr">
         <is>
@@ -1729,7 +1841,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="48" customHeight="1" s="18">
       <c r="B17" s="33" t="inlineStr">
         <is>
@@ -1737,7 +1848,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="63.75" customHeight="1" s="18">
       <c r="B19" s="33" t="inlineStr">
         <is>
@@ -1745,7 +1855,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="21.75" customHeight="1" s="18">
       <c r="B21" s="32" t="inlineStr">
         <is>
@@ -1760,7 +1869,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="48" customHeight="1" s="18">
       <c r="B24" s="33" t="inlineStr">
         <is>
@@ -1768,7 +1876,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="31.5" customHeight="1" s="18">
       <c r="B26" s="33" t="inlineStr">
         <is>
@@ -1776,7 +1883,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="18" customHeight="1" s="18">
       <c r="B28" s="33" t="inlineStr">
         <is>
@@ -1812,7 +1918,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="21.75" customHeight="1" s="18">
       <c r="B34" s="32" t="inlineStr">
         <is>
@@ -1855,7 +1960,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="21.75" customHeight="1" s="18">
       <c r="B41" s="32" t="inlineStr">
         <is>
@@ -1898,11 +2002,24 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48" ht="18" customHeight="1" s="18">
       <c r="B48" s="33" t="inlineStr">
         <is>
           <t>© Acqlerate — Defense Acquisitions Academy. For training use only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="36" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
         </is>
       </c>
     </row>
